--- a/연구코드/results/feature_selection/gangnam/step2_vif.xlsx
+++ b/연구코드/results/feature_selection/gangnam/step2_vif.xlsx
@@ -22,10 +22,10 @@
     <t>VIF</t>
   </si>
   <si>
+    <t>min</t>
+  </si>
+  <si>
     <t>max</t>
-  </si>
-  <si>
-    <t>min</t>
   </si>
   <si>
     <t>range</t>
@@ -555,7 +555,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>4342.40411706348</v>
+        <v>4342.404117067667</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -563,7 +563,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>1682.290401536478</v>
+        <v>1682.290401537106</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -579,7 +579,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>595.9846117539803</v>
+        <v>595.9846117540986</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -587,7 +587,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>566.2138795577548</v>
+        <v>566.2138795586446</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -595,7 +595,7 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>558.4367085560835</v>
+        <v>558.436708557053</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -603,7 +603,7 @@
         <v>11</v>
       </c>
       <c r="B11">
-        <v>480.0729428774733</v>
+        <v>480.0729428775501</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -611,7 +611,7 @@
         <v>12</v>
       </c>
       <c r="B12">
-        <v>454.6220680693093</v>
+        <v>454.6220680693781</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -627,7 +627,7 @@
         <v>14</v>
       </c>
       <c r="B14">
-        <v>304.3615276909626</v>
+        <v>304.3615276910346</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -635,7 +635,7 @@
         <v>15</v>
       </c>
       <c r="B15">
-        <v>249.5686071976911</v>
+        <v>249.5686071977256</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -651,7 +651,7 @@
         <v>17</v>
       </c>
       <c r="B17">
-        <v>194.258271392882</v>
+        <v>194.2582713928903</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -659,7 +659,7 @@
         <v>18</v>
       </c>
       <c r="B18">
-        <v>153.3845763081509</v>
+        <v>153.3845763081665</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -667,7 +667,7 @@
         <v>19</v>
       </c>
       <c r="B19">
-        <v>138.2878417312995</v>
+        <v>138.2878417316179</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -675,7 +675,7 @@
         <v>20</v>
       </c>
       <c r="B20">
-        <v>130.887968726462</v>
+        <v>130.8879687265438</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -683,7 +683,7 @@
         <v>21</v>
       </c>
       <c r="B21">
-        <v>83.51115754331592</v>
+        <v>83.51115754332133</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -691,7 +691,7 @@
         <v>22</v>
       </c>
       <c r="B22">
-        <v>75.68636973120091</v>
+        <v>75.68636973166326</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -699,7 +699,7 @@
         <v>23</v>
       </c>
       <c r="B23">
-        <v>72.60456492038352</v>
+        <v>72.60456492039522</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -707,7 +707,7 @@
         <v>24</v>
       </c>
       <c r="B24">
-        <v>51.66726992578948</v>
+        <v>51.66726992580963</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -715,7 +715,7 @@
         <v>25</v>
       </c>
       <c r="B25">
-        <v>51.20380519536801</v>
+        <v>51.20380519536888</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -723,7 +723,7 @@
         <v>26</v>
       </c>
       <c r="B26">
-        <v>46.8376088705339</v>
+        <v>46.83760887053438</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -731,7 +731,7 @@
         <v>27</v>
       </c>
       <c r="B27">
-        <v>43.03454590897858</v>
+        <v>43.03454590898187</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -739,7 +739,7 @@
         <v>28</v>
       </c>
       <c r="B28">
-        <v>30.76301699509802</v>
+        <v>30.76301699510516</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -747,7 +747,7 @@
         <v>29</v>
       </c>
       <c r="B29">
-        <v>27.17469332567154</v>
+        <v>27.17469332568114</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -755,7 +755,7 @@
         <v>30</v>
       </c>
       <c r="B30">
-        <v>25.61494581798397</v>
+        <v>25.61494581798696</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -763,7 +763,7 @@
         <v>31</v>
       </c>
       <c r="B31">
-        <v>23.51796923824291</v>
+        <v>23.51796923824315</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -771,7 +771,7 @@
         <v>32</v>
       </c>
       <c r="B32">
-        <v>21.40264452519091</v>
+        <v>21.40264452519152</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -779,7 +779,7 @@
         <v>33</v>
       </c>
       <c r="B33">
-        <v>19.95387756390497</v>
+        <v>19.95387756392349</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -787,7 +787,7 @@
         <v>34</v>
       </c>
       <c r="B34">
-        <v>19.75841772858955</v>
+        <v>19.7584177285912</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -795,7 +795,7 @@
         <v>35</v>
       </c>
       <c r="B35">
-        <v>17.69489186968478</v>
+        <v>17.69489186969374</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -803,7 +803,7 @@
         <v>36</v>
       </c>
       <c r="B36">
-        <v>16.54251136074845</v>
+        <v>16.54251136076972</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -811,7 +811,7 @@
         <v>37</v>
       </c>
       <c r="B37">
-        <v>15.43429234615727</v>
+        <v>15.43429234615746</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -819,7 +819,7 @@
         <v>38</v>
       </c>
       <c r="B38">
-        <v>15.39444461607886</v>
+        <v>15.39444461608752</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -827,7 +827,7 @@
         <v>39</v>
       </c>
       <c r="B39">
-        <v>14.94003159495474</v>
+        <v>14.94003159502051</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -835,7 +835,7 @@
         <v>40</v>
       </c>
       <c r="B40">
-        <v>14.57347062388141</v>
+        <v>14.57347062388143</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -843,7 +843,7 @@
         <v>41</v>
       </c>
       <c r="B41">
-        <v>12.36219577347118</v>
+        <v>12.36219577347191</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -851,7 +851,7 @@
         <v>42</v>
       </c>
       <c r="B42">
-        <v>11.95349113270823</v>
+        <v>11.95349113271388</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -859,7 +859,7 @@
         <v>43</v>
       </c>
       <c r="B43">
-        <v>8.395187298679479</v>
+        <v>8.395187298679879</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -867,7 +867,7 @@
         <v>44</v>
       </c>
       <c r="B44">
-        <v>6.528992849223204</v>
+        <v>6.528992849223355</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -875,7 +875,7 @@
         <v>45</v>
       </c>
       <c r="B45">
-        <v>5.662198183163771</v>
+        <v>5.662198183164302</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -883,7 +883,7 @@
         <v>46</v>
       </c>
       <c r="B46">
-        <v>4.020147437395202</v>
+        <v>4.020147437396045</v>
       </c>
     </row>
   </sheetData>

--- a/연구코드/results/feature_selection/gangnam/step2_vif.xlsx
+++ b/연구코드/results/feature_selection/gangnam/step2_vif.xlsx
@@ -22,10 +22,10 @@
     <t>VIF</t>
   </si>
   <si>
+    <t>max</t>
+  </si>
+  <si>
     <t>min</t>
-  </si>
-  <si>
-    <t>max</t>
   </si>
   <si>
     <t>range</t>
@@ -555,7 +555,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>4342.404117067667</v>
+        <v>4342.40411706348</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -563,7 +563,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>1682.290401537106</v>
+        <v>1682.290401536478</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -579,7 +579,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>595.9846117540986</v>
+        <v>595.9846117539803</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -587,7 +587,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>566.2138795586446</v>
+        <v>566.2138795577548</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -595,7 +595,7 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>558.436708557053</v>
+        <v>558.4367085560835</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -603,7 +603,7 @@
         <v>11</v>
       </c>
       <c r="B11">
-        <v>480.0729428775501</v>
+        <v>480.0729428774733</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -611,7 +611,7 @@
         <v>12</v>
       </c>
       <c r="B12">
-        <v>454.6220680693781</v>
+        <v>454.6220680693093</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -627,7 +627,7 @@
         <v>14</v>
       </c>
       <c r="B14">
-        <v>304.3615276910346</v>
+        <v>304.3615276909626</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -635,7 +635,7 @@
         <v>15</v>
       </c>
       <c r="B15">
-        <v>249.5686071977256</v>
+        <v>249.5686071976911</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -651,7 +651,7 @@
         <v>17</v>
       </c>
       <c r="B17">
-        <v>194.2582713928903</v>
+        <v>194.258271392882</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -659,7 +659,7 @@
         <v>18</v>
       </c>
       <c r="B18">
-        <v>153.3845763081665</v>
+        <v>153.3845763081509</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -667,7 +667,7 @@
         <v>19</v>
       </c>
       <c r="B19">
-        <v>138.2878417316179</v>
+        <v>138.2878417312995</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -675,7 +675,7 @@
         <v>20</v>
       </c>
       <c r="B20">
-        <v>130.8879687265438</v>
+        <v>130.887968726462</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -683,7 +683,7 @@
         <v>21</v>
       </c>
       <c r="B21">
-        <v>83.51115754332133</v>
+        <v>83.51115754331592</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -691,7 +691,7 @@
         <v>22</v>
       </c>
       <c r="B22">
-        <v>75.68636973166326</v>
+        <v>75.68636973120091</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -699,7 +699,7 @@
         <v>23</v>
       </c>
       <c r="B23">
-        <v>72.60456492039522</v>
+        <v>72.60456492038352</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -707,7 +707,7 @@
         <v>24</v>
       </c>
       <c r="B24">
-        <v>51.66726992580963</v>
+        <v>51.66726992578948</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -715,7 +715,7 @@
         <v>25</v>
       </c>
       <c r="B25">
-        <v>51.20380519536888</v>
+        <v>51.20380519536801</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -723,7 +723,7 @@
         <v>26</v>
       </c>
       <c r="B26">
-        <v>46.83760887053438</v>
+        <v>46.8376088705339</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -731,7 +731,7 @@
         <v>27</v>
       </c>
       <c r="B27">
-        <v>43.03454590898187</v>
+        <v>43.03454590897858</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -739,7 +739,7 @@
         <v>28</v>
       </c>
       <c r="B28">
-        <v>30.76301699510516</v>
+        <v>30.76301699509802</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -747,7 +747,7 @@
         <v>29</v>
       </c>
       <c r="B29">
-        <v>27.17469332568114</v>
+        <v>27.17469332567154</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -755,7 +755,7 @@
         <v>30</v>
       </c>
       <c r="B30">
-        <v>25.61494581798696</v>
+        <v>25.61494581798397</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -763,7 +763,7 @@
         <v>31</v>
       </c>
       <c r="B31">
-        <v>23.51796923824315</v>
+        <v>23.51796923824291</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -771,7 +771,7 @@
         <v>32</v>
       </c>
       <c r="B32">
-        <v>21.40264452519152</v>
+        <v>21.40264452519091</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -779,7 +779,7 @@
         <v>33</v>
       </c>
       <c r="B33">
-        <v>19.95387756392349</v>
+        <v>19.95387756390497</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -787,7 +787,7 @@
         <v>34</v>
       </c>
       <c r="B34">
-        <v>19.7584177285912</v>
+        <v>19.75841772858955</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -795,7 +795,7 @@
         <v>35</v>
       </c>
       <c r="B35">
-        <v>17.69489186969374</v>
+        <v>17.69489186968478</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -803,7 +803,7 @@
         <v>36</v>
       </c>
       <c r="B36">
-        <v>16.54251136076972</v>
+        <v>16.54251136074845</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -811,7 +811,7 @@
         <v>37</v>
       </c>
       <c r="B37">
-        <v>15.43429234615746</v>
+        <v>15.43429234615727</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -819,7 +819,7 @@
         <v>38</v>
       </c>
       <c r="B38">
-        <v>15.39444461608752</v>
+        <v>15.39444461607886</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -827,7 +827,7 @@
         <v>39</v>
       </c>
       <c r="B39">
-        <v>14.94003159502051</v>
+        <v>14.94003159495474</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -835,7 +835,7 @@
         <v>40</v>
       </c>
       <c r="B40">
-        <v>14.57347062388143</v>
+        <v>14.57347062388141</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -843,7 +843,7 @@
         <v>41</v>
       </c>
       <c r="B41">
-        <v>12.36219577347191</v>
+        <v>12.36219577347118</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -851,7 +851,7 @@
         <v>42</v>
       </c>
       <c r="B42">
-        <v>11.95349113271388</v>
+        <v>11.95349113270823</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -859,7 +859,7 @@
         <v>43</v>
       </c>
       <c r="B43">
-        <v>8.395187298679879</v>
+        <v>8.395187298679479</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -867,7 +867,7 @@
         <v>44</v>
       </c>
       <c r="B44">
-        <v>6.528992849223355</v>
+        <v>6.528992849223204</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -875,7 +875,7 @@
         <v>45</v>
       </c>
       <c r="B45">
-        <v>5.662198183164302</v>
+        <v>5.662198183163771</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -883,7 +883,7 @@
         <v>46</v>
       </c>
       <c r="B46">
-        <v>4.020147437396045</v>
+        <v>4.020147437395202</v>
       </c>
     </row>
   </sheetData>
